--- a/data/trans_dic/P1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,98</t>
+          <t>2,26; 5,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,0</t>
+          <t>0,65; 3,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 10,19</t>
+          <t>4,61; 10,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 10,86</t>
+          <t>1,55; 10,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,63</t>
+          <t>0,96; 3,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,35</t>
+          <t>2,26; 6,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 10,2</t>
+          <t>5,08; 10,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 8,47</t>
+          <t>2,49; 8,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,17</t>
+          <t>1,92; 4,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,16</t>
+          <t>1,65; 4,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,41</t>
+          <t>5,55; 9,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,36</t>
+          <t>2,57; 7,91</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,15</t>
+          <t>5,29; 9,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 12,46</t>
+          <t>7,75; 12,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,22; 13,22</t>
+          <t>8,24; 13,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,26; 21,23</t>
+          <t>12,15; 21,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,84</t>
+          <t>2,6; 5,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,54</t>
+          <t>3,0; 6,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,85</t>
+          <t>5,29; 9,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 11,09</t>
+          <t>4,66; 11,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,91</t>
+          <t>4,35; 6,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,92</t>
+          <t>5,99; 8,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 10,88</t>
+          <t>7,45; 10,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 14,18</t>
+          <t>8,52; 14,41</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,44</t>
+          <t>4,42; 8,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,4</t>
+          <t>3,26; 6,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,6; 13,7</t>
+          <t>8,63; 13,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,06; 18,53</t>
+          <t>12,48; 19,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,51</t>
+          <t>1,19; 3,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,89</t>
+          <t>0,8; 3,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,29</t>
+          <t>2,95; 6,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,4</t>
+          <t>3,97; 7,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,24</t>
+          <t>3,04; 5,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,19</t>
+          <t>2,32; 4,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 9,26</t>
+          <t>6,42; 9,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,28; 12,28</t>
+          <t>8,51; 12,4</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,62</t>
+          <t>4,25; 8,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 11,38</t>
+          <t>6,36; 11,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,42; 15,97</t>
+          <t>10,36; 16,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 21,58</t>
+          <t>6,08; 21,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 7,01</t>
+          <t>3,1; 7,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,78</t>
+          <t>3,2; 6,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,62</t>
+          <t>3,9; 7,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,48</t>
+          <t>5,36; 8,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,09</t>
+          <t>4,13; 7,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 8,37</t>
+          <t>5,15; 8,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 11,01</t>
+          <t>7,58; 11,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 14,02</t>
+          <t>6,87; 14,17</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 9,96</t>
+          <t>4,44; 9,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 10,02</t>
+          <t>4,88; 10,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,88; 14,84</t>
+          <t>8,64; 14,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,67; 23,25</t>
+          <t>16,35; 22,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 11,85</t>
+          <t>6,04; 11,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 11,53</t>
+          <t>5,99; 11,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,38; 19,32</t>
+          <t>12,02; 18,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,48; 19,41</t>
+          <t>14,62; 19,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 9,92</t>
+          <t>5,9; 9,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,99</t>
+          <t>6,07; 9,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,19; 15,85</t>
+          <t>11,16; 15,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,8; 20,65</t>
+          <t>16,67; 20,67</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,58; 13,47</t>
+          <t>6,2; 13,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,82; 16,43</t>
+          <t>8,59; 16,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,43; 20,31</t>
+          <t>12,51; 20,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,8; 25,53</t>
+          <t>18,48; 25,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,65; 26,04</t>
+          <t>17,92; 25,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,6; 29,06</t>
+          <t>19,53; 28,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,52; 29,91</t>
+          <t>20,32; 29,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,17; 34,04</t>
+          <t>9,96; 34,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,53; 19,04</t>
+          <t>13,56; 19,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15,38; 21,32</t>
+          <t>15,46; 21,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,75; 23,94</t>
+          <t>17,93; 23,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,73; 28,26</t>
+          <t>11,89; 28,56</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,8; 26,6</t>
+          <t>15,15; 26,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,42; 28,4</t>
+          <t>17,21; 28,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,54; 31,43</t>
+          <t>21,61; 31,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,19; 36,08</t>
+          <t>27,38; 35,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,64; 40,1</t>
+          <t>29,34; 39,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,88; 42,76</t>
+          <t>32,57; 42,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,2; 46,15</t>
+          <t>34,39; 45,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>52,68; 59,33</t>
+          <t>52,51; 59,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24,96; 32,7</t>
+          <t>25,24; 33,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,7; 35,7</t>
+          <t>28,06; 35,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,96; 39,01</t>
+          <t>30,95; 39,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,26; 48,87</t>
+          <t>43,56; 48,9</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,17</t>
+          <t>6,35; 8,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,36; 9,4</t>
+          <t>7,37; 9,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,55; 13,76</t>
+          <t>11,37; 13,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,92; 18,61</t>
+          <t>13,45; 18,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,8; 9,81</t>
+          <t>7,82; 9,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,9; 10,99</t>
+          <t>8,98; 11,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,92; 14,4</t>
+          <t>12,02; 14,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,16; 17,75</t>
+          <t>13,28; 17,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,68</t>
+          <t>7,42; 8,71</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,47; 9,87</t>
+          <t>8,48; 9,94</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,02; 13,74</t>
+          <t>12,02; 13,69</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,29; 17,84</t>
+          <t>14,35; 17,84</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11456; 29559</t>
+          <t>11157; 29406</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2868; 13643</t>
+          <t>2961; 14131</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19829; 42755</t>
+          <t>19342; 42547</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6340; 43437</t>
+          <t>6199; 41391</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4621; 16951</t>
+          <t>4504; 15887</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9513; 27336</t>
+          <t>9718; 27404</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20015; 40350</t>
+          <t>20091; 41358</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7797; 26529</t>
+          <t>7786; 26293</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17663; 40084</t>
+          <t>18432; 40386</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15854; 36776</t>
+          <t>14568; 35563</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45040; 76672</t>
+          <t>45264; 76105</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18519; 52490</t>
+          <t>18330; 56404</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36858; 67328</t>
+          <t>38905; 67015</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53377; 85632</t>
+          <t>53261; 85714</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48547; 78092</t>
+          <t>48651; 78514</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51940; 89935</t>
+          <t>51466; 89008</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15560; 36548</t>
+          <t>16257; 36774</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17726; 39932</t>
+          <t>18310; 40370</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31861; 55499</t>
+          <t>29796; 53474</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23548; 56798</t>
+          <t>23873; 56380</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59955; 94080</t>
+          <t>59144; 94571</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75481; 115691</t>
+          <t>77680; 116274</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87420; 125523</t>
+          <t>86004; 123865</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80276; 132718</t>
+          <t>79722; 134868</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27792; 53916</t>
+          <t>28203; 53035</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22377; 43672</t>
+          <t>22205; 45063</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57564; 91656</t>
+          <t>57728; 89765</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64685; 99379</t>
+          <t>66921; 103572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8404; 24196</t>
+          <t>8216; 24080</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5762; 20547</t>
+          <t>5676; 21384</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21144; 41589</t>
+          <t>19481; 40699</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22718; 43790</t>
+          <t>23478; 45121</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40991; 69593</t>
+          <t>40403; 71493</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30389; 58335</t>
+          <t>32345; 60112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84084; 123213</t>
+          <t>85453; 124963</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93374; 138574</t>
+          <t>96064; 139943</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21360; 44725</t>
+          <t>22065; 45221</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39013; 69969</t>
+          <t>39081; 71027</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67298; 103168</t>
+          <t>66930; 106562</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57150; 191573</t>
+          <t>54010; 191743</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15850; 36133</t>
+          <t>15971; 37070</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18851; 41786</t>
+          <t>19727; 43002</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24366; 49470</t>
+          <t>25322; 49794</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37802; 60483</t>
+          <t>38180; 59808</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41968; 73328</t>
+          <t>42747; 73842</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66184; 103074</t>
+          <t>63416; 101680</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>96937; 142620</t>
+          <t>98157; 142986</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>103956; 224484</t>
+          <t>109971; 226860</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17574; 38531</t>
+          <t>17157; 37592</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21119; 43027</t>
+          <t>20971; 43644</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42440; 70913</t>
+          <t>41279; 71585</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93542; 130505</t>
+          <t>91770; 128186</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25828; 47881</t>
+          <t>24409; 47416</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27603; 51624</t>
+          <t>26809; 51921</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61533; 95973</t>
+          <t>59704; 93862</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>79338; 106327</t>
+          <t>80108; 107926</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47841; 78445</t>
+          <t>46625; 76417</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54127; 87670</t>
+          <t>53240; 87300</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>109034; 154529</t>
+          <t>108811; 154562</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>186323; 229045</t>
+          <t>184857; 229211</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19238; 39398</t>
+          <t>18126; 38405</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27309; 50886</t>
+          <t>26619; 50855</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41543; 67898</t>
+          <t>41826; 67605</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69232; 93994</t>
+          <t>68035; 94717</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>60532; 89312</t>
+          <t>61462; 89127</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69369; 102865</t>
+          <t>69123; 100558</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77535; 112979</t>
+          <t>76780; 111836</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>55814; 207103</t>
+          <t>60579; 207109</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>85993; 121023</t>
+          <t>86158; 121315</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>102079; 141513</t>
+          <t>102650; 144316</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>126381; 170486</t>
+          <t>127665; 169909</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>114506; 275953</t>
+          <t>116077; 278946</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>33157; 55835</t>
+          <t>31795; 54567</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43515; 70946</t>
+          <t>43003; 71496</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55357; 80775</t>
+          <t>55537; 81371</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76879; 102018</t>
+          <t>77405; 100815</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>95625; 133898</t>
+          <t>97965; 132137</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>127884; 166322</t>
+          <t>126703; 165492</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>140846; 184685</t>
+          <t>137628; 183530</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>224307; 252627</t>
+          <t>223598; 251915</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>135749; 177845</t>
+          <t>137229; 180517</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>176988; 228062</t>
+          <t>179234; 228674</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>203471; 256336</t>
+          <t>203407; 256751</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>306526; 346289</t>
+          <t>308654; 346469</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>209536; 267820</t>
+          <t>208080; 268121</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>252379; 322286</t>
+          <t>252517; 323157</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>391908; 467061</t>
+          <t>385915; 462648</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>446849; 643924</t>
+          <t>465285; 645945</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>263461; 331569</t>
+          <t>264324; 329422</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>316856; 391205</t>
+          <t>319615; 393320</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>422524; 510518</t>
+          <t>426087; 512579</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>488579; 659073</t>
+          <t>493102; 660438</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>489298; 577801</t>
+          <t>494099; 579992</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>591395; 689537</t>
+          <t>592116; 694341</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>834114; 953145</t>
+          <t>834380; 950192</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1025000; 1279680</t>
+          <t>1029354; 1279637</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,95</t>
+          <t>2,17; 5,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,11</t>
+          <t>0,59; 3,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 10,14</t>
+          <t>4,92; 10,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 10,35</t>
+          <t>3,22; 12,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,4</t>
+          <t>0,81; 3,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,37</t>
+          <t>2,25; 6,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 10,45</t>
+          <t>5,03; 10,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 8,39</t>
+          <t>2,46; 8,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,2</t>
+          <t>1,75; 4,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,02</t>
+          <t>1,73; 4,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 9,34</t>
+          <t>5,38; 9,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,91</t>
+          <t>3,48; 8,66</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 9,11</t>
+          <t>5,23; 9,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 12,47</t>
+          <t>7,98; 12,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 13,3</t>
+          <t>8,22; 13,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,15; 21,01</t>
+          <t>12,08; 20,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,88</t>
+          <t>2,38; 5,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,62</t>
+          <t>3,07; 6,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 9,49</t>
+          <t>5,62; 9,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,66; 11,01</t>
+          <t>6,54; 11,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 6,95</t>
+          <t>4,35; 6,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,96</t>
+          <t>5,92; 9,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,73</t>
+          <t>7,54; 10,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,52; 14,41</t>
+          <t>9,86; 14,72</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,3</t>
+          <t>4,42; 8,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,61</t>
+          <t>3,15; 6,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,63; 13,42</t>
+          <t>8,68; 13,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,48; 19,31</t>
+          <t>12,77; 19,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,49</t>
+          <t>1,14; 3,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,01</t>
+          <t>0,79; 2,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,15</t>
+          <t>3,04; 6,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,62</t>
+          <t>4,24; 7,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 5,38</t>
+          <t>3,06; 5,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,32</t>
+          <t>2,28; 4,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 9,39</t>
+          <t>6,3; 9,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 12,4</t>
+          <t>9,14; 12,82</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,71</t>
+          <t>4,12; 8,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 11,56</t>
+          <t>6,46; 11,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,36; 16,49</t>
+          <t>10,3; 15,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,08; 21,6</t>
+          <t>17,34; 24,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,19</t>
+          <t>3,03; 7,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,98</t>
+          <t>3,16; 6,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,67</t>
+          <t>3,71; 7,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,39</t>
+          <t>6,03; 8,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,14</t>
+          <t>3,96; 6,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,26</t>
+          <t>5,14; 8,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,58; 11,04</t>
+          <t>7,63; 10,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 14,17</t>
+          <t>12,14; 15,77</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 9,72</t>
+          <t>4,27; 9,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,88; 10,16</t>
+          <t>4,79; 9,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,64; 14,98</t>
+          <t>8,91; 15,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,35; 22,84</t>
+          <t>16,84; 23,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 11,74</t>
+          <t>6,03; 11,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,99; 11,59</t>
+          <t>5,99; 11,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,02; 18,89</t>
+          <t>12,25; 18,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,62; 19,7</t>
+          <t>14,35; 19,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,66</t>
+          <t>6,14; 10,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,95</t>
+          <t>6,21; 10,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,16; 15,86</t>
+          <t>11,16; 15,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,67; 20,67</t>
+          <t>16,37; 20,14</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,2; 13,13</t>
+          <t>6,21; 13,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,59; 16,42</t>
+          <t>8,07; 16,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,51; 20,22</t>
+          <t>12,31; 20,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,48; 25,73</t>
+          <t>18,23; 24,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,92; 25,99</t>
+          <t>17,6; 26,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,53; 28,41</t>
+          <t>18,96; 28,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,32; 29,6</t>
+          <t>20,71; 29,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,96; 34,04</t>
+          <t>29,45; 36,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,56; 19,09</t>
+          <t>13,27; 18,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15,46; 21,74</t>
+          <t>15,66; 22,22</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,93; 23,86</t>
+          <t>17,54; 23,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,89; 28,56</t>
+          <t>25,08; 30,09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,15; 26,0</t>
+          <t>15,46; 26,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,21; 28,62</t>
+          <t>17,63; 28,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,61; 31,66</t>
+          <t>21,21; 31,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,38; 35,65</t>
+          <t>26,88; 35,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,34; 39,57</t>
+          <t>29,19; 40,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,57; 42,55</t>
+          <t>32,09; 42,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,39; 45,86</t>
+          <t>35,41; 46,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>52,51; 59,16</t>
+          <t>52,46; 58,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,24; 33,2</t>
+          <t>25,12; 32,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,06; 35,8</t>
+          <t>27,53; 35,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,95; 39,07</t>
+          <t>30,93; 38,95</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,56; 48,9</t>
+          <t>43,01; 48,41</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,18</t>
+          <t>6,39; 8,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,43</t>
+          <t>7,45; 9,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,37; 13,63</t>
+          <t>11,37; 13,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,45; 18,67</t>
+          <t>17,04; 19,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,82; 9,75</t>
+          <t>7,74; 9,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,98; 11,05</t>
+          <t>8,95; 11,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,02; 14,46</t>
+          <t>12,04; 14,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,28; 17,79</t>
+          <t>16,56; 18,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,71</t>
+          <t>7,36; 8,75</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,48; 9,94</t>
+          <t>8,53; 9,9</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,02; 13,69</t>
+          <t>12,0; 13,69</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,35; 17,84</t>
+          <t>17,19; 18,85</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>26890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>17079</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31342</t>
+          <t>43969</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11157; 29406</t>
+          <t>10712; 29329</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2961; 14131</t>
+          <t>2676; 13962</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19342; 42547</t>
+          <t>20652; 43978</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6199; 41391</t>
+          <t>13130; 49858</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4504; 15887</t>
+          <t>3805; 15620</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9718; 27404</t>
+          <t>9664; 27045</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20091; 41358</t>
+          <t>19910; 40788</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7786; 26293</t>
+          <t>8920; 30729</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18432; 40386</t>
+          <t>16797; 39240</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14568; 35563</t>
+          <t>15279; 36773</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45264; 76105</t>
+          <t>43822; 74747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18330; 56404</t>
+          <t>26773; 66730</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67680</t>
+          <t>75783</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39990</t>
+          <t>44031</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>107670</t>
+          <t>119815</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38905; 67015</t>
+          <t>38450; 68249</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53261; 85714</t>
+          <t>54844; 88896</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48651; 78514</t>
+          <t>48540; 79046</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51466; 89008</t>
+          <t>57593; 98192</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16257; 36774</t>
+          <t>14885; 34971</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18310; 40370</t>
+          <t>18728; 40120</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29796; 53474</t>
+          <t>31687; 54515</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23873; 56380</t>
+          <t>32800; 59704</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59144; 94571</t>
+          <t>59207; 93120</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77680; 116274</t>
+          <t>76811; 117221</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86004; 123865</t>
+          <t>86980; 123520</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>79722; 134868</t>
+          <t>96509; 144035</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83029</t>
+          <t>98670</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>35942</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>116372</t>
+          <t>134612</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28203; 53035</t>
+          <t>28203; 54010</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22205; 45063</t>
+          <t>21502; 43137</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57728; 89765</t>
+          <t>58064; 91404</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66921; 103572</t>
+          <t>79276; 120030</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8216; 24080</t>
+          <t>7861; 23252</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5676; 21384</t>
+          <t>5602; 21224</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19481; 40699</t>
+          <t>20103; 40816</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23478; 45121</t>
+          <t>26407; 47144</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40403; 71493</t>
+          <t>40705; 72426</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32345; 60112</t>
+          <t>31734; 57634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85453; 124963</t>
+          <t>83871; 122893</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96064; 139943</t>
+          <t>113727; 159500</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>132097</t>
+          <t>144754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>49120</t>
+          <t>54609</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>181217</t>
+          <t>199363</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22065; 45221</t>
+          <t>21403; 44911</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39081; 71027</t>
+          <t>39689; 71221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66930; 106562</t>
+          <t>66518; 102108</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54010; 191743</t>
+          <t>121455; 169145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15971; 37070</t>
+          <t>15620; 36285</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19727; 43002</t>
+          <t>19456; 41916</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25322; 49794</t>
+          <t>24107; 49502</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38180; 59808</t>
+          <t>44459; 66160</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42747; 73842</t>
+          <t>41005; 72294</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63416; 101680</t>
+          <t>63271; 102606</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>98157; 142986</t>
+          <t>98803; 141167</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>109971; 226860</t>
+          <t>174507; 226747</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111632</t>
+          <t>121036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>93351</t>
+          <t>101959</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>204983</t>
+          <t>222995</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17157; 37592</t>
+          <t>16507; 37754</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20971; 43644</t>
+          <t>20570; 42883</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41279; 71585</t>
+          <t>42581; 71800</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91770; 128186</t>
+          <t>102632; 141818</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24409; 47416</t>
+          <t>24374; 46912</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26809; 51921</t>
+          <t>26839; 52575</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59704; 93862</t>
+          <t>60864; 94260</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80108; 107926</t>
+          <t>87379; 116148</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46625; 76417</t>
+          <t>48565; 81319</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53240; 87300</t>
+          <t>54500; 89649</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108811; 154562</t>
+          <t>108812; 155848</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>184857; 229211</t>
+          <t>199402; 245338</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80300</t>
+          <t>88099</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>132880</t>
+          <t>143912</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>213180</t>
+          <t>232011</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18126; 38405</t>
+          <t>18161; 39185</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26619; 50855</t>
+          <t>24997; 51817</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41826; 67605</t>
+          <t>41157; 68944</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>68035; 94717</t>
+          <t>74203; 101651</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>61462; 89127</t>
+          <t>60369; 89600</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69123; 100558</t>
+          <t>67135; 101891</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>76780; 111836</t>
+          <t>78225; 111879</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>60579; 207109</t>
+          <t>129345; 158308</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>86158; 121315</t>
+          <t>84313; 120001</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>102650; 144316</t>
+          <t>103946; 147506</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>127665; 169909</t>
+          <t>124875; 169171</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>116077; 278946</t>
+          <t>212279; 254599</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88396</t>
+          <t>95744</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>238741</t>
+          <t>260002</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>327138</t>
+          <t>355746</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31795; 54567</t>
+          <t>32458; 55267</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43003; 71496</t>
+          <t>44058; 70664</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55537; 81371</t>
+          <t>54511; 80816</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>77405; 100815</t>
+          <t>83382; 110575</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>97965; 132137</t>
+          <t>97472; 135280</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>126703; 165492</t>
+          <t>124811; 165759</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>137628; 183530</t>
+          <t>141683; 185513</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>223598; 251915</t>
+          <t>243723; 274088</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>137229; 180517</t>
+          <t>136615; 179380</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>179234; 228674</t>
+          <t>175870; 227433</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>203407; 256751</t>
+          <t>203262; 255983</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>308654; 346469</t>
+          <t>333220; 375094</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>579391</t>
+          <t>650977</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>602510</t>
+          <t>657534</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1181902</t>
+          <t>1308510</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>208080; 268121</t>
+          <t>209412; 271884</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>252517; 323157</t>
+          <t>255201; 322954</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>385915; 462648</t>
+          <t>385870; 468053</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>465285; 645945</t>
+          <t>601919; 699677</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>264324; 329422</t>
+          <t>261588; 329584</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>319615; 393320</t>
+          <t>318571; 393250</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>426087; 512579</t>
+          <t>426715; 512088</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>493102; 660438</t>
+          <t>618777; 694281</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>494099; 579992</t>
+          <t>489979; 582606</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>592116; 694341</t>
+          <t>595702; 691765</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>834380; 950192</t>
+          <t>832352; 950207</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1029354; 1279637</t>
+          <t>1249391; 1369989</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
+          <t>Población que conforma un hogar unipersonal (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
+          <t>Población que conforma un hogar unipersonal (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
